--- a/Results/TestCases/XLSX/pim_TestCases.xlsx
+++ b/Results/TestCases/XLSX/pim_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="72">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -72,19 +72,25 @@
     <t>High</t>
   </si>
   <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>TC_PIM_02</t>
+  </si>
+  <si>
+    <t>Search employee details</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>TC_PIM_03</t>
+  </si>
+  <si>
+    <t>Update employee information</t>
+  </si>
+  <si>
     <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>TC_PIM_02</t>
-  </si>
-  <si>
-    <t>Search employee details</t>
-  </si>
-  <si>
-    <t>TC_PIM_03</t>
-  </si>
-  <si>
-    <t>Update employee information</t>
   </si>
   <si>
     <t>TC_PIM_04</t>
@@ -229,7 +235,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -249,12 +255,24 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF107C41"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFA51D24"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF5A6268"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -264,6 +282,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF7919"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1E7DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -310,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -319,6 +347,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -774,13 +808,13 @@
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>19</v>
+      <c r="K3" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -789,13 +823,13 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -809,13 +843,13 @@
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
+      <c r="K4" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -824,13 +858,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -842,15 +876,15 @@
         <v>17</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -859,13 +893,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -877,15 +911,15 @@
         <v>17</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -894,13 +928,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -912,15 +946,15 @@
         <v>17</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -929,13 +963,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -947,15 +981,15 @@
         <v>17</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -964,13 +998,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -982,15 +1016,15 @@
         <v>17</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -999,13 +1033,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -1017,15 +1051,15 @@
         <v>17</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1034,13 +1068,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -1052,15 +1086,15 @@
         <v>17</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1069,13 +1103,13 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -1087,15 +1121,15 @@
         <v>17</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1104,13 +1138,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1122,15 +1156,15 @@
         <v>17</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1139,13 +1173,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1157,15 +1191,15 @@
         <v>17</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1174,13 +1208,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1192,15 +1226,15 @@
         <v>17</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1209,13 +1243,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1227,15 +1261,15 @@
         <v>17</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1244,13 +1278,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -1262,15 +1296,15 @@
         <v>17</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1279,13 +1313,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -1297,15 +1331,15 @@
         <v>17</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1314,13 +1348,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -1332,15 +1366,15 @@
         <v>17</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1349,13 +1383,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1367,15 +1401,15 @@
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1384,13 +1418,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1402,15 +1436,15 @@
         <v>17</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1419,13 +1453,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1437,15 +1471,15 @@
         <v>17</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1454,13 +1488,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1472,15 +1506,15 @@
         <v>17</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1489,13 +1523,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1507,15 +1541,15 @@
         <v>17</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1524,13 +1558,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1542,15 +1576,15 @@
         <v>17</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1559,13 +1593,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1577,10 +1611,10 @@
         <v>17</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Results/TestCases/XLSX/pim_TestCases.xlsx
+++ b/Results/TestCases/XLSX/pim_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="100">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,15 +58,13 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The user is logged in to OrangeHRM with valid credentials and the Dashboard has loaded. The user has navigated to the 'PIM' module.</t>
+  </si>
+  <si>
+    <t>1. Perform the actions described in the test title</t>
+  </si>
+  <si>
+    <t>- The first row id should display the text 'testEmployeeId'</t>
   </si>
   <si>
     <t>High</t>
@@ -81,16 +79,19 @@
     <t>Search employee details</t>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
     <t>TC_PIM_03</t>
   </si>
   <si>
     <t>Update employee information</t>
   </si>
   <si>
-    <t>SKIPPED</t>
+    <t>1. Click the edit button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The first row id should display the text 'testEmployeeId'
+- The employee id input should have the value 'testEmployeeId'
+- The Nickname field should have the value 'testNickname'
+- The Other Id field should have the value 'testNickname'</t>
   </si>
   <si>
     <t>TC_PIM_04</t>
@@ -99,6 +100,9 @@
     <t>Delete employee records</t>
   </si>
   <si>
+    <t>- The table rows should have a count of '0'</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -108,54 +112,89 @@
     <t>Verify PIM search with non-existent employee ID returns no records</t>
   </si>
   <si>
+    <t>- The 'No Records Found' element should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_06</t>
   </si>
   <si>
     <t>Verify PIM Employee List tab loads correctly</t>
   </si>
   <si>
+    <t>1. Click the employee list tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The search employee id input should be visible
+- The Search button should be visible
+- The Reset Password button should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_07</t>
   </si>
   <si>
     <t>Verify PIM top menu has Configuration tab</t>
   </si>
   <si>
+    <t>- The 'Configuration' element should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_08</t>
   </si>
   <si>
     <t>Verify PIM top menu has Reports tab</t>
   </si>
   <si>
+    <t>- The 'Reports' element should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_09</t>
   </si>
   <si>
     <t>Verify PIM top menu has Optional Fields menu</t>
   </si>
   <si>
+    <t>1. Click the 'Configuration' element</t>
+  </si>
+  <si>
+    <t>- The 'Optional Fields' element should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_10</t>
   </si>
   <si>
     <t>Verify PIM top menu has Custom Fields menu</t>
   </si>
   <si>
+    <t>- The 'Custom Fields' element should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_11</t>
   </si>
   <si>
     <t>Verify PIM top menu has Data Import menu</t>
   </si>
   <si>
+    <t>- The 'Data Import' element should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_12</t>
   </si>
   <si>
     <t>Verify PIM top menu has Reporting Methods menu</t>
   </si>
   <si>
+    <t>- The 'Reporting Methods' element should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_13</t>
   </si>
   <si>
     <t>Verify PIM top menu has Termination Reasons menu</t>
   </si>
   <si>
+    <t>- The 'Termination Reasons' element should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_14</t>
   </si>
   <si>
@@ -165,77 +204,131 @@
     <t>Negative</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the add employee tab
+2. Click the Save button</t>
+  </si>
+  <si>
+    <t>- The 'Employee Full Name' element should display the text 'Required'</t>
+  </si>
+  <si>
     <t>TC_PIM_15</t>
   </si>
   <si>
     <t>Verify validation error on empty Last Name input</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the add employee tab
+2. Enter 'TestFirst' into the First Name field
+3. Click the Save button</t>
+  </si>
+  <si>
     <t>TC_PIM_16</t>
   </si>
   <si>
     <t>Verify Create Login Details switch toggle is visible</t>
   </si>
   <si>
+    <t>1. Click the add employee tab</t>
+  </si>
+  <si>
+    <t>- The toggle should be present in the DOM</t>
+  </si>
+  <si>
     <t>TC_PIM_17</t>
   </si>
   <si>
     <t>Verify Cancel button on Add Employee form returns to employee list</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the add employee tab
+2. Click the oxd button  ghost element</t>
+  </si>
+  <si>
+    <t>- The page.url() should contain '/pim/viewEmployeeList'</t>
+  </si>
+  <si>
     <t>TC_PIM_18</t>
   </si>
   <si>
     <t>Verify table checkboxes exist for employee rows</t>
   </si>
   <si>
+    <t>- The check should be present</t>
+  </si>
+  <si>
     <t>TC_PIM_19</t>
   </si>
   <si>
     <t>Verify reset button clears Employee Id search field</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the employee list tab
+2. Enter '12345' into the search employee id input
+3. Click the Reset Password button</t>
+  </si>
+  <si>
+    <t>- The search employee id input should have the value ''</t>
+  </si>
+  <si>
     <t>TC_PIM_20</t>
   </si>
   <si>
     <t>Verify PIM breadcrumb title contains PIM</t>
   </si>
   <si>
+    <t>- The breadcrumb should contain the text 'PIM'</t>
+  </si>
+  <si>
     <t>TC_PIM_21</t>
   </si>
   <si>
     <t>Verify job title dropdown is functional in search form</t>
   </si>
   <si>
+    <t>- The 'Job Title' element should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_22</t>
   </si>
   <si>
     <t>Verify sub unit dropdown is functional in search form</t>
   </si>
   <si>
+    <t>- The 'Sub Unit' element should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_23</t>
   </si>
   <si>
     <t>Verify employment status dropdown is functional in search form</t>
   </si>
   <si>
+    <t>- The 'Employment Status' element should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_24</t>
   </si>
   <si>
     <t>Verify supervisor name input autocomplete has autocomplete attributes</t>
   </si>
   <si>
+    <t>- The 'Supervisor Name' element should be visible</t>
+  </si>
+  <si>
     <t>TC_PIM_25</t>
   </si>
   <si>
     <t>Verify add employee photoupload element has file type input attribute</t>
+  </si>
+  <si>
+    <t>- The file element should be present in the DOM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -259,20 +352,8 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FFA51D24"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF5A6268"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,16 +368,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1E7DD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -338,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -347,12 +418,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -808,43 +873,43 @@
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>22</v>
+      <c r="K3" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
+      <c r="K4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -873,18 +938,18 @@
         <v>16</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -893,13 +958,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -908,18 +973,18 @@
         <v>16</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -928,33 +993,33 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -963,13 +1028,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -978,18 +1043,18 @@
         <v>16</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -998,13 +1063,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -1013,18 +1078,18 @@
         <v>16</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1033,33 +1098,33 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1068,33 +1133,33 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1103,33 +1168,33 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1138,68 +1203,68 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1208,33 +1273,33 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1243,33 +1308,33 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1278,33 +1343,33 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1313,33 +1378,33 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1348,33 +1413,33 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1383,33 +1448,33 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1418,13 +1483,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1433,18 +1498,18 @@
         <v>16</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1453,13 +1518,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1468,18 +1533,18 @@
         <v>16</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1488,13 +1553,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1503,18 +1568,18 @@
         <v>16</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1523,13 +1588,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1538,18 +1603,18 @@
         <v>16</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1558,13 +1623,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1573,18 +1638,18 @@
         <v>16</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1593,28 +1658,28 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Results/TestCases/XLSX/pim_TestCases.xlsx
+++ b/Results/TestCases/XLSX/pim_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="101">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -70,13 +70,16 @@
     <t>High</t>
   </si>
   <si>
-    <t>PASSED</t>
+    <t>FAILED</t>
   </si>
   <si>
     <t>TC_PIM_02</t>
   </si>
   <si>
     <t>Search employee details</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
   </si>
   <si>
     <t>TC_PIM_03</t>
@@ -328,7 +331,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -348,12 +351,18 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF107C41"/>
+      <color rgb="FFA51D24"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF5A6268"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,7 +376,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1E7DD"/>
+        <fgColor rgb="FFF8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E3E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -409,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -418,6 +432,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -873,13 +890,13 @@
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>19</v>
+      <c r="K3" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -888,33 +905,33 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
+      <c r="K4" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -923,13 +940,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -938,18 +955,18 @@
         <v>16</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -958,13 +975,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -973,18 +990,18 @@
         <v>16</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -993,33 +1010,33 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -1028,13 +1045,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -1043,18 +1060,18 @@
         <v>16</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -1063,13 +1080,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -1078,18 +1095,18 @@
         <v>16</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1098,33 +1115,33 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1133,33 +1150,33 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1168,33 +1185,33 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1203,33 +1220,33 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1238,33 +1255,33 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1273,68 +1290,68 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="J16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1343,33 +1360,33 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1378,33 +1395,33 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1413,33 +1430,33 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1448,33 +1465,33 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1483,13 +1500,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1498,18 +1515,18 @@
         <v>16</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1518,13 +1535,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1533,18 +1550,18 @@
         <v>16</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1553,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1568,18 +1585,18 @@
         <v>16</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1588,13 +1605,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1603,18 +1620,18 @@
         <v>16</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1623,13 +1640,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1638,18 +1655,18 @@
         <v>16</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1658,28 +1675,28 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
